--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715920BC-30C5-44CA-A2F9-BE49938BAFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B4AB30-332C-4019-B20B-55E50BA9E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -128,6 +128,48 @@
   </si>
   <si>
     <t>Ahmed Abdelaziz Tracking</t>
+  </si>
+  <si>
+    <t>Mohamed Ibrahim</t>
+  </si>
+  <si>
+    <t>Alaa Ibrahim Ahmed Ibrahim</t>
+  </si>
+  <si>
+    <t>Alaa Nasr</t>
+  </si>
+  <si>
+    <t>Ashraf Adel Ahmed</t>
+  </si>
+  <si>
+    <t>El Sayed Mohamed</t>
+  </si>
+  <si>
+    <t>Hassan Hemaida</t>
+  </si>
+  <si>
+    <t>Islam Reda</t>
+  </si>
+  <si>
+    <t>Reda Mohamed Bayomy</t>
+  </si>
+  <si>
+    <t>Tamer Khalil</t>
+  </si>
+  <si>
+    <t>Khaled Adel</t>
+  </si>
+  <si>
+    <t>Abdallah mohamed</t>
+  </si>
+  <si>
+    <t>Alaa Mohamed Ibrahim</t>
+  </si>
+  <si>
+    <t>Islam Eid</t>
+  </si>
+  <si>
+    <t>Driver Name</t>
   </si>
 </sst>
 </file>
@@ -137,7 +179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$EGP]\ #,##0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,16 +187,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -162,11 +224,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -178,11 +285,25 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -285,10 +406,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D14" totalsRowShown="0">
   <autoFilter ref="A1:D14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="8">
       <calculatedColumnFormula>Table3[[#This Row],[Salary]]/26</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -562,7 +683,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" bestFit="1" customWidth="1"/>
@@ -570,9 +691,10 @@
     <col min="3" max="3" width="11.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,8 +707,11 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G1" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -600,8 +725,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>307.69230769230768</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G2" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -615,8 +743,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>326.92307692307691</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -630,8 +761,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>403.84615384615387</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G4" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -645,8 +779,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>423.07692307692309</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G5" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -660,8 +797,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>365.38461538461536</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -675,8 +815,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>392.30769230769232</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G7" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -690,8 +833,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>42.307692307692307</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G8" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -705,8 +851,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>365.38461538461536</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G9" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -720,8 +869,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>576.92307692307691</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G10" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -735,8 +887,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>442.30769230769232</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -750,8 +905,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>461.53846153846155</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G12" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -765,8 +923,11 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>376.92307692307691</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G13" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -780,22 +941,28 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>269.23076923076923</v>
       </c>
+      <c r="G14" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G14">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B4AB30-332C-4019-B20B-55E50BA9E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823CAE0F-15C8-488B-99CB-7E334EC393C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
   <sheets>
     <sheet name="Salaries" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>https://docs.google.com/spreadsheets/d/1TGCT-VLkvCR46JAcw6f2foi-NbowKZpuuoPIYbcKCyE/edit?gid=1510773283#gid=1510773283</t>
   </si>
   <si>
-    <t>https://docs.google.com/spreadsheets/d/1-nTDvCd2AjQDrp7EUFLmEyHQSHe_wMYDXmeAFihfcY0/edit?gid=463135065#gid=463135065</t>
-  </si>
-  <si>
     <t>Ashraf Tracking</t>
   </si>
   <si>
@@ -170,6 +167,9 @@
   </si>
   <si>
     <t>Driver Name</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1-nTDvCd2AjQDrp7EUFLmEyHQSHe_wMYDXmeAFihfcY0/edit?gid=1150286976#gid=1150286976</t>
   </si>
 </sst>
 </file>
@@ -405,6 +405,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D14" totalsRowShown="0">
   <autoFilter ref="A1:D14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
+    <sortCondition ref="A1:A14"/>
+  </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="10"/>
@@ -708,7 +711,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -726,7 +729,7 @@
         <v>307.69230769230768</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -744,208 +747,211 @@
         <v>326.92307692307691</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4">
-        <v>5004447589419</v>
+        <v>5022146847419</v>
       </c>
       <c r="C4" s="3">
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="D4" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>403.84615384615387</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>36</v>
+        <v>376.92307692307691</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4">
-        <v>5022701624419</v>
+        <v>5004447589419</v>
       </c>
       <c r="C5" s="3">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="D5" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>423.07692307692309</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>37</v>
+        <v>403.84615384615387</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="4">
-        <v>5022188204419</v>
+        <v>5022701624419</v>
       </c>
       <c r="C6" s="3">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="D6" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>365.38461538461536</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>38</v>
+        <v>423.07692307692309</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>5022383642419</v>
+        <v>5022188204419</v>
       </c>
       <c r="C7" s="3">
-        <v>10200</v>
+        <v>9500</v>
       </c>
       <c r="D7" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>392.30769230769232</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>39</v>
+        <v>365.38461538461536</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>5004738816419</v>
+        <v>5022383642419</v>
       </c>
       <c r="C8" s="3">
-        <v>1100</v>
+        <v>10200</v>
       </c>
       <c r="D8" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>42.307692307692307</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>40</v>
+        <v>392.30769230769232</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>5022225671419</v>
+        <v>5004738816419</v>
       </c>
       <c r="C9" s="3">
-        <v>9500</v>
+        <v>1100</v>
       </c>
       <c r="D9" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>365.38461538461536</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>41</v>
+        <v>42.307692307692307</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4">
-        <v>5004890383419</v>
+        <v>5022195252419</v>
       </c>
       <c r="C10" s="3">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="D10" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>576.92307692307691</v>
+        <v>269.23076923076923</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4">
-        <v>5004446575419</v>
+        <v>5022225671419</v>
       </c>
       <c r="C11" s="3">
-        <v>11500</v>
+        <v>9500</v>
       </c>
       <c r="D11" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>442.30769230769232</v>
+        <v>365.38461538461536</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
+        <v>5004890383419</v>
       </c>
       <c r="C12" s="3">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="D12" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>461.53846153846155</v>
+        <v>576.92307692307691</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
-        <v>5022146847419</v>
+        <v>5004446575419</v>
       </c>
       <c r="C13" s="3">
-        <v>9800</v>
+        <v>11500</v>
       </c>
       <c r="D13" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>376.92307692307691</v>
+        <v>442.30769230769232</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4">
-        <v>5022195252419</v>
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C14" s="3">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="D14" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>269.23076923076923</v>
+        <v>461.53846153846155</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G14">
+    <sortCondition ref="G1:G14"/>
+  </sortState>
   <conditionalFormatting sqref="A2:A3">
     <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
@@ -977,7 +983,7 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="114.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -999,50 +1005,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823CAE0F-15C8-488B-99CB-7E334EC393C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66447643-36EB-40FF-838F-51DBF93AC684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
   <sheets>
     <sheet name="Salaries" sheetId="1" r:id="rId1"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66447643-36EB-40FF-838F-51DBF93AC684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77BBD70-5185-4558-A575-21CD10B7B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/1-nTDvCd2AjQDrp7EUFLmEyHQSHe_wMYDXmeAFihfcY0/edit?gid=1150286976#gid=1150286976</t>
+  </si>
+  <si>
+    <t>Mahmoud Waheed Abd El-Razek</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -403,16 +446,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D14" totalsRowShown="0">
-  <autoFilter ref="A1:D14" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
-    <sortCondition ref="A1:A14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D15" totalsRowShown="0">
+  <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
+    <sortCondition ref="A1:A15"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="12">
       <calculatedColumnFormula>Table3[[#This Row],[Salary]]/26</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -686,7 +729,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" bestFit="1" customWidth="1"/>
@@ -860,17 +903,15 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="4">
-        <v>5022195252419</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="3">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="D10" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>269.23076923076923</v>
+        <v>461.53846153846155</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>39</v>
@@ -878,17 +919,17 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4">
-        <v>5022225671419</v>
+        <v>5022195252419</v>
       </c>
       <c r="C11" s="3">
-        <v>9500</v>
+        <v>7000</v>
       </c>
       <c r="D11" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>365.38461538461536</v>
+        <v>269.23076923076923</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>42</v>
@@ -896,17 +937,17 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>5004890383419</v>
+        <v>5022225671419</v>
       </c>
       <c r="C12" s="3">
-        <v>15000</v>
+        <v>9500</v>
       </c>
       <c r="D12" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>576.92307692307691</v>
+        <v>365.38461538461536</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>33</v>
@@ -914,17 +955,17 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>5004446575419</v>
+        <v>5004890383419</v>
       </c>
       <c r="C13" s="3">
-        <v>11500</v>
+        <v>15000</v>
       </c>
       <c r="D13" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>442.30769230769232</v>
+        <v>576.92307692307691</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>40</v>
@@ -932,20 +973,35 @@
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>5004446575419</v>
       </c>
       <c r="C14" s="3">
-        <v>12000</v>
+        <v>11500</v>
       </c>
       <c r="D14" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>461.53846153846155</v>
+        <v>442.30769230769232</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3">
+        <v>12000</v>
+      </c>
+      <c r="D15" s="3">
+        <f>Table3[[#This Row],[Salary]]/26</f>
+        <v>461.53846153846155</v>
       </c>
     </row>
   </sheetData>
@@ -953,22 +1009,22 @@
     <sortCondition ref="G1:G14"/>
   </sortState>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A14">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+  <conditionalFormatting sqref="A2:A15">
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G14">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77BBD70-5185-4558-A575-21CD10B7B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FAE012-2048-4261-99B2-6A5DAC4B41DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -296,47 +296,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -452,10 +412,10 @@
     <sortCondition ref="A1:A15"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="8">
       <calculatedColumnFormula>Table3[[#This Row],[Salary]]/26</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -891,11 +851,11 @@
         <v>5004738816419</v>
       </c>
       <c r="C9" s="3">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="D9" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>42.307692307692307</v>
+        <v>423.07692307692309</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>45</v>
@@ -1009,22 +969,22 @@
     <sortCondition ref="G1:G14"/>
   </sortState>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A15">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G14">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Task Tracking System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Tracking &amp; Financial Controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FAE012-2048-4261-99B2-6A5DAC4B41DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D4F668-7E81-4804-AE88-3F982CE550A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>Mahmoud Waheed Abd El-Razek</t>
+  </si>
+  <si>
+    <t>Mena Najeh</t>
   </si>
 </sst>
 </file>
@@ -963,6 +966,9 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>461.53846153846155</v>
       </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G14">

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Tracking &amp; Financial Controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D4F668-7E81-4804-AE88-3F982CE550A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E870E6F-2F71-47AD-9E52-BECB72974AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -800,11 +800,11 @@
         <v>5022701624419</v>
       </c>
       <c r="C6" s="3">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="D6" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>423.07692307692309</v>
+        <v>461.53846153846155</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>36</v>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Tracking &amp; Financial Controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E870E6F-2F71-47AD-9E52-BECB72974AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D669A66-F3D9-44E0-867C-A0787123BEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Mena Najeh</t>
+  </si>
+  <si>
+    <t>Magdy Ramadan Ebd El-Kerem</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" bestFit="1" customWidth="1"/>
@@ -968,6 +971,11 @@
       </c>
       <c r="G15" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/list.xlsx
+++ b/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\Claude Projects\Visual Studio\Telecom Department\Tracking &amp; Financial Controller\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Claude Projects\Visual Studio\Telecom Department\Tracking &amp; Financial Controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D669A66-F3D9-44E0-867C-A0787123BEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4A1C01-49AF-4F53-AA94-FE3715230955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB18FD28-8304-47B6-A714-5A0F1E7D9244}"/>
   </bookViews>
   <sheets>
     <sheet name="Salaries" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Name</t>
   </si>
@@ -61,15 +61,9 @@
     <t>Mahmoud Elsharawi Fathey</t>
   </si>
   <si>
-    <t>Mohamed Shehata</t>
-  </si>
-  <si>
     <t>Mostafa Ahmed Mohamed</t>
   </si>
   <si>
-    <t>Sameh Abd El Fatah Ebada</t>
-  </si>
-  <si>
     <t>Yousry Mohamed Hekel</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
     <t>Ahmed Abdelaziz Tracking</t>
   </si>
   <si>
-    <t>Mohamed Ibrahim</t>
-  </si>
-  <si>
     <t>Alaa Ibrahim Ahmed Ibrahim</t>
   </si>
   <si>
@@ -139,33 +130,15 @@
     <t>Ashraf Adel Ahmed</t>
   </si>
   <si>
-    <t>El Sayed Mohamed</t>
-  </si>
-  <si>
     <t>Hassan Hemaida</t>
   </si>
   <si>
     <t>Islam Reda</t>
   </si>
   <si>
-    <t>Reda Mohamed Bayomy</t>
-  </si>
-  <si>
     <t>Tamer Khalil</t>
   </si>
   <si>
-    <t>Khaled Adel</t>
-  </si>
-  <si>
-    <t>Abdallah mohamed</t>
-  </si>
-  <si>
-    <t>Alaa Mohamed Ibrahim</t>
-  </si>
-  <si>
-    <t>Islam Eid</t>
-  </si>
-  <si>
     <t>Driver Name</t>
   </si>
   <si>
@@ -179,6 +152,9 @@
   </si>
   <si>
     <t>Magdy Ramadan Ebd El-Kerem</t>
+  </si>
+  <si>
+    <t>Islam Ibrahim</t>
   </si>
 </sst>
 </file>
@@ -188,7 +164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$EGP]\ #,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,8 +180,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,14 +200,8 @@
         <bgColor theme="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -248,41 +224,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -295,24 +241,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -412,16 +346,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D15" totalsRowShown="0">
-  <autoFilter ref="A1:D15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
-    <sortCondition ref="A1:A15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABB4DA97-EBC5-4BD2-B2DC-7C263647DF38}" name="Table3" displayName="Table3" ref="A1:D13" totalsRowShown="0">
+  <autoFilter ref="A1:D13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
+    <sortCondition ref="A1:A13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{5C281241-C008-4D25-A002-12725B498A5D}" name="Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{DCCEF508-DD76-4DD3-9377-B18D9EF15C1D}" name="Account Number" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{ADDC6F5A-CEB2-46E1-9477-CD55E5CB2983}" name="Salary" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{892E467E-0F8C-4F38-ACE1-EBC3D4D94CA9}" name="Salary/Day" dataDxfId="7">
       <calculatedColumnFormula>Table3[[#This Row],[Salary]]/26</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -695,7 +629,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" bestFit="1" customWidth="1"/>
@@ -720,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -737,8 +671,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>307.69230769230768</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>43</v>
+      <c r="G2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -755,13 +689,13 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>326.92307692307691</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>34</v>
+      <c r="G3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4">
         <v>5022146847419</v>
@@ -773,8 +707,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>376.92307692307691</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>44</v>
+      <c r="G4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -791,8 +725,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>403.84615384615387</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>35</v>
+      <c r="G5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -809,8 +743,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>461.53846153846155</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
+      <c r="G6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -827,8 +761,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>365.38461538461536</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>37</v>
+      <c r="G7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -845,8 +779,8 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>392.30769230769232</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>38</v>
+      <c r="G8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -863,13 +797,13 @@
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>423.07692307692309</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>45</v>
+      <c r="G9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="3">
@@ -880,12 +814,12 @@
         <v>461.53846153846155</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4">
         <v>5022195252419</v>
@@ -896,9 +830,6 @@
       <c r="D11" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
         <v>269.23076923076923</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -906,99 +837,49 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>5022225671419</v>
+        <v>5004890383419</v>
       </c>
       <c r="C12" s="3">
-        <v>9500</v>
+        <v>15000</v>
       </c>
       <c r="D12" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>365.38461538461536</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>33</v>
+        <v>576.92307692307691</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
-        <v>5004890383419</v>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="D13" s="3">
         <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>576.92307692307691</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4">
-        <v>5004446575419</v>
-      </c>
-      <c r="C14" s="3">
-        <v>11500</v>
-      </c>
-      <c r="D14" s="3">
-        <f>Table3[[#This Row],[Salary]]/26</f>
-        <v>442.30769230769232</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3">
-        <v>12000</v>
-      </c>
-      <c r="D15" s="3">
-        <f>Table3[[#This Row],[Salary]]/26</f>
         <v>461.53846153846155</v>
       </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G16" t="s">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G14">
-    <sortCondition ref="G1:G14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G6">
+    <sortCondition ref="G1:G6"/>
   </sortState>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A15">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1019,66 +900,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
